--- a/artfynd/A 54345-2025 artfynd.xlsx
+++ b/artfynd/A 54345-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>110679778</v>
       </c>
       <c r="B2" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519595.2934323865</v>
+        <v>519595</v>
       </c>
       <c r="R2" t="n">
-        <v>7160974.607898449</v>
+        <v>7160975</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,32 +772,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110679776</v>
+        <v>110679779</v>
       </c>
       <c r="B3" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519616.4250907793</v>
+        <v>519616</v>
       </c>
       <c r="R3" t="n">
-        <v>7160967.866828212</v>
+        <v>7161125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110679779</v>
+        <v>110679777</v>
       </c>
       <c r="B4" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519616.2731794389</v>
+        <v>519595</v>
       </c>
       <c r="R4" t="n">
-        <v>7161124.752433548</v>
+        <v>7160975</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110679777</v>
+        <v>110679776</v>
       </c>
       <c r="B5" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519595.2934323865</v>
+        <v>519616</v>
       </c>
       <c r="R5" t="n">
-        <v>7160974.607898449</v>
+        <v>7160968</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
